--- a/evals/unit_tests_comparative/test06_conv_gap_exceeds_roofline/analysis_output_ref/perf_report_trace2.xlsx
+++ b/evals/unit_tests_comparative/test06_conv_gap_exceeds_roofline/analysis_output_ref/perf_report_trace2.xlsx
@@ -11,7 +11,8 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,15 +971,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>call_stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::convolution</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aten::convolution =&gt; aten::convolution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
@@ -1111,10 +1168,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1198,7 +1260,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'cudnn::engines::spatial_convolution_2d&lt;cudnn::ConvFwdAlgoImplicitPrecompGemm, float&gt;', 'stream': 7, 'gpu_op_uid': 5, 'count': 1, 'total_duration_us': np.float64(40.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(40.0), 'median_duration_us': np.float64(40.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(40.0), 'max_duration_us': np.float64(40.0)}]</t>
+          <t>[{'name': 'cudnn::engines::spatial_convolution_2d&lt;cudnn::ConvFwdAlgoImplicitPrecompGemm, float&gt;', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(40.0), 'gpu_op_uids': [5], 'mean_duration_us': np.float64(40.0), 'median_duration_us': np.float64(40.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(40.0), 'max_duration_us': np.float64(40.0)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1210,10 +1272,15 @@
       <c r="AA2" t="b">
         <v>1</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>aten::convolution =&gt; aten::convolution</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
         <v>100</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>100</v>
       </c>
     </row>
